--- a/results_task_1/glm/5_Y_N_TN_2.xlsx
+++ b/results_task_1/glm/5_Y_N_TN_2.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5_Y_N*glm-5.3*TN_2.xlsx</t>
+          <t>5_Y_N_TN_2.xlsx</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5_Y_N*glm-5.3*TN_2.xlsx</t>
+          <t>5_Y_N_TN_2.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -635,7 +635,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5_Y_N*glm-5.3*TN_2.xlsx</t>
+          <t>5_Y_N_TN_2.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
